--- a/Result/profitability/6109.xlsx
+++ b/Result/profitability/6109.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,7 +672,7 @@
         <v>-0.34625</v>
       </c>
       <c r="N2" t="n">
-        <v>18.71875</v>
+        <v>18.9575</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>-0.28</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.32625</v>
+        <v>-0.2825</v>
       </c>
       <c r="N3" t="n">
-        <v>17.25375</v>
+        <v>19.42625</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.1</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.24</v>
+        <v>-0.24625</v>
       </c>
       <c r="N4" t="n">
-        <v>18.85125</v>
+        <v>19.42</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1021,7 +1021,7 @@
         <v>-0.25</v>
       </c>
       <c r="N5" t="n">
-        <v>18.2</v>
+        <v>18.37</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.24</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.225</v>
+        <v>-0.26125</v>
       </c>
       <c r="N6" t="n">
-        <v>17.545</v>
+        <v>17.355</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.15</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.225</v>
+        <v>-0.285</v>
       </c>
       <c r="N7" t="n">
-        <v>17.1625</v>
+        <v>16.15375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.38</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1825</v>
+        <v>-0.2075</v>
       </c>
       <c r="N8" t="n">
-        <v>17.33875</v>
+        <v>17.0025</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>0.45</v>
       </c>
       <c r="M11" t="n">
-        <v>0.05249999999999999</v>
+        <v>0.0525</v>
       </c>
       <c r="N11" t="n">
         <v>16.34125</v>
@@ -1899,7 +1899,7 @@
         <v>-0.05</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05874999999999999</v>
+        <v>0.05875</v>
       </c>
       <c r="N12" t="n">
         <v>16.11375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6109</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>221</v>
+      </c>
+      <c r="D75" t="n">
+        <v>176</v>
+      </c>
+      <c r="E75" t="n">
+        <v>45</v>
+      </c>
+      <c r="F75" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-19</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-8.68%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-18</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-37</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-37</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.35625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.795</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.8333333333333335</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.690000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1164502164502165</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.359999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.07139107611548545</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
